--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487962_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487962_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.841900000000001</v>
+        <v>9.3117</v>
       </c>
       <c r="E2" t="n">
-        <v>9.882199999999999</v>
+        <v>10.352</v>
       </c>
       <c r="F2" t="n">
         <v>-1.0403</v>
@@ -610,10 +610,10 @@
         <v>2.1805</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2848</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.2369</v>
+        <v>-0.767</v>
       </c>
       <c r="U2" t="n">
         <v>-0.0479</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.7718</v>
+        <v>6.047</v>
       </c>
       <c r="E3" t="n">
-        <v>6.3996</v>
+        <v>5.5452</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3722</v>
+        <v>0.5018</v>
       </c>
       <c r="G3" t="n">
         <v>4.9699</v>
@@ -688,13 +688,13 @@
         <v>1.9822</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6058</v>
+        <v>0.8809</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0501</v>
+        <v>0.1956</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5557</v>
+        <v>0.6853</v>
       </c>
       <c r="V3" t="n">
         <v>0.1962</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9075</v>
+        <v>3.9565</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2639</v>
+        <v>6.0602</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.3564</v>
+        <v>-2.1037</v>
       </c>
       <c r="G4" t="n">
         <v>3.723</v>
@@ -766,13 +766,13 @@
         <v>1.1893</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2529</v>
+        <v>0.3019</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.132</v>
+        <v>-0.3358</v>
       </c>
       <c r="U4" t="n">
-        <v>0.385</v>
+        <v>0.6377</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2666</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6079</v>
+        <v>3.9374</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8851</v>
+        <v>4.355</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2773</v>
+        <v>-0.4177</v>
       </c>
       <c r="G5" t="n">
         <v>-0.0532</v>
@@ -844,13 +844,13 @@
         <v>1.9822</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8058</v>
+        <v>-0.4763</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0497</v>
+        <v>-0.5798</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2439</v>
+        <v>0.1035</v>
       </c>
       <c r="V5" t="n">
         <v>2.4846</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1344</v>
+        <v>1.2291</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6605</v>
+        <v>2.5586</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5261</v>
+        <v>-1.3295</v>
       </c>
       <c r="G6" t="n">
         <v>0.463</v>
@@ -922,13 +922,13 @@
         <v>1.1893</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.181</v>
+        <v>-0.0863</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3192</v>
+        <v>-0.4211</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1383</v>
+        <v>0.3348</v>
       </c>
       <c r="V6" t="n">
         <v>-0.337</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3709</v>
+        <v>0.399</v>
       </c>
       <c r="E8" t="n">
         <v>0.6859</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.315</v>
+        <v>-0.2869</v>
       </c>
       <c r="G8" t="n">
         <v>0.7597</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3888</v>
+        <v>-0.3607</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3888</v>
+        <v>-0.3607</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1034</v>
+        <v>-0.0015</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.6175</v>
       </c>
       <c r="F9" t="n">
         <v>-0.619</v>
@@ -1156,10 +1156,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3561</v>
+        <v>-0.2542</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1248</v>
+        <v>-0.0229</v>
       </c>
       <c r="U9" t="n">
         <v>-0.2313</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3002</v>
+        <v>-0.3188</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.3178</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8612</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>1.4537</v>
@@ -1234,13 +1234,13 @@
         <v>0.9911</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0799</v>
+        <v>-1.0985</v>
       </c>
       <c r="T10" t="n">
-        <v>0.06619999999999999</v>
+        <v>-0.177</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1461</v>
+        <v>-0.9215</v>
       </c>
       <c r="V10" t="n">
         <v>-0.674</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.8668</v>
+        <v>-0.5508</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0432</v>
+        <v>-0.8394</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1763</v>
+        <v>0.2886</v>
       </c>
       <c r="G12" t="n">
         <v>0.324</v>
@@ -1390,13 +1390,13 @@
         <v>0.9911</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8538</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.624</v>
+        <v>-0.4202</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2299</v>
+        <v>-0.1176</v>
       </c>
       <c r="V12" t="n">
         <v>-0.337</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.3662</v>
+        <v>-0.8859</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8816000000000001</v>
+        <v>1.2496</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2478</v>
+        <v>-2.1355</v>
       </c>
       <c r="G13" t="n">
         <v>1.7029</v>
@@ -1468,13 +1468,13 @@
         <v>1.1893</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8025</v>
+        <v>-0.3222</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5505</v>
+        <v>-0.1825</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2519</v>
+        <v>-0.1396</v>
       </c>
       <c r="V13" t="n">
         <v>-1.4737</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.1272</v>
+        <v>-1.9411</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.6408</v>
+        <v>-0.5389</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4864</v>
+        <v>-1.4022</v>
       </c>
       <c r="G14" t="n">
         <v>-0.8404</v>
@@ -1546,13 +1546,13 @@
         <v>0.1982</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2779</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2155</v>
+        <v>-0.1313</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2071</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>21.2861</v>
+        <v>21.59810000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>30.9347</v>
+        <v>31.2468</v>
       </c>
       <c r="F15" t="n">
-        <v>-9.648699999999998</v>
+        <v>-9.6487</v>
       </c>
       <c r="G15" t="n">
         <v>21.55240000000001</v>
@@ -1624,13 +1624,13 @@
         <v>11.8932</v>
       </c>
       <c r="S15" t="n">
-        <v>-3.5059</v>
+        <v>-3.194</v>
       </c>
       <c r="T15" t="n">
-        <v>-3.0456</v>
+        <v>-2.7336</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4601999999999996</v>
+        <v>-0.4603</v>
       </c>
       <c r="V15" t="n">
         <v>0.2665000000000002</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ CANTERO</t>
+          <t>A. MIR AMATE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.7038</v>
+        <v>4.0112</v>
       </c>
       <c r="E16" t="n">
-        <v>7.392</v>
+        <v>3.3683</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.6882</v>
+        <v>0.6428</v>
       </c>
       <c r="G16" t="n">
-        <v>3.6762</v>
+        <v>3.3669</v>
       </c>
       <c r="H16" t="n">
-        <v>5.6374</v>
+        <v>-1.1369</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.9612</v>
+        <v>4.5038</v>
       </c>
       <c r="J16" t="n">
-        <v>7.808</v>
+        <v>3.7491</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6473</v>
+        <v>0.2018</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1607</v>
+        <v>3.5473</v>
       </c>
       <c r="M16" t="n">
-        <v>-4.1318</v>
+        <v>-0.3822</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.0099</v>
+        <v>-1.3386</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.1219</v>
+        <v>0.9565</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.7929</v>
+        <v>0.3964</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9822</v>
+        <v>-0.1982</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1893</v>
+        <v>0.5947</v>
       </c>
       <c r="S16" t="n">
-        <v>3.0276</v>
+        <v>0.2478</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2997</v>
+        <v>-0.1825</v>
       </c>
       <c r="U16" t="n">
-        <v>1.728</v>
+        <v>0.4303</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. MIR AMATE</t>
+          <t>J. RODRIGUEZ CANTERO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3732</v>
+        <v>3.1262</v>
       </c>
       <c r="E17" t="n">
-        <v>3.0627</v>
+        <v>6.5771</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3105</v>
+        <v>-3.4509</v>
       </c>
       <c r="G17" t="n">
-        <v>3.3669</v>
+        <v>3.6762</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.1369</v>
+        <v>5.6374</v>
       </c>
       <c r="I17" t="n">
-        <v>4.5038</v>
+        <v>-1.9612</v>
       </c>
       <c r="J17" t="n">
-        <v>3.7491</v>
+        <v>7.808</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2018</v>
+        <v>7.6473</v>
       </c>
       <c r="L17" t="n">
-        <v>3.5473</v>
+        <v>0.1607</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3822</v>
+        <v>-4.1318</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3386</v>
+        <v>-2.0099</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9565</v>
+        <v>-2.1219</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3964</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1982</v>
+        <v>-1.9822</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5947</v>
+        <v>1.1893</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3902</v>
+        <v>1.45</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4881</v>
+        <v>0.4847</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0979</v>
+        <v>0.9653</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="18">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3811</v>
+        <v>0.5729</v>
       </c>
       <c r="E19" t="n">
-        <v>4.4705</v>
+        <v>4.9798</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.8516</v>
+        <v>-4.4069</v>
       </c>
       <c r="G19" t="n">
         <v>-1.7135</v>
@@ -1936,13 +1936,13 @@
         <v>1.5858</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2712</v>
+        <v>0.6828</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3082</v>
+        <v>0.2012</v>
       </c>
       <c r="U19" t="n">
-        <v>0.037</v>
+        <v>0.4817</v>
       </c>
       <c r="V19" t="n">
         <v>1.2071</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7168</v>
+        <v>-0.5869</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0643</v>
+        <v>0.0376</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6526</v>
+        <v>-0.6245000000000001</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8090000000000001</v>
@@ -2014,13 +2014,13 @@
         <v>0.1982</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1061</v>
+        <v>0.0239</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1248</v>
+        <v>-0.0229</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. PEREZ GARCIA</t>
+          <t>H. TAVIO SOLIS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4537</v>
+        <v>-1.9529</v>
       </c>
       <c r="E21" t="n">
-        <v>2.4926</v>
+        <v>-1.2037</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.9464</v>
+        <v>-0.7491</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3222</v>
+        <v>-2.8701</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0428</v>
+        <v>-1.1004</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2794</v>
+        <v>-1.7696</v>
       </c>
       <c r="J21" t="n">
-        <v>5.1543</v>
+        <v>-1.1974</v>
       </c>
       <c r="K21" t="n">
-        <v>2.5026</v>
+        <v>0.0404</v>
       </c>
       <c r="L21" t="n">
-        <v>2.6517</v>
+        <v>-1.2377</v>
       </c>
       <c r="M21" t="n">
-        <v>-5.4765</v>
+        <v>-1.6727</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.5454</v>
+        <v>-1.1408</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.9312</v>
+        <v>-0.5319</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.3787</v>
+        <v>0.1982</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.1716</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7929</v>
+        <v>0.1982</v>
       </c>
       <c r="S21" t="n">
-        <v>1.725</v>
+        <v>0.045</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9877</v>
+        <v>-0.0064</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7373</v>
+        <v>0.0514</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.4778</v>
+        <v>0.674</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.4778</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H. TAVIO SOLIS</t>
+          <t>A. PEREZ GARCIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3708</v>
+        <v>-2.238</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5094</v>
+        <v>1.8814</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8615</v>
+        <v>-4.1194</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.8701</v>
+        <v>-0.3222</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1004</v>
+        <v>-0.0428</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.7696</v>
+        <v>-0.2794</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.1974</v>
+        <v>5.1543</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0404</v>
+        <v>2.5026</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2377</v>
+        <v>2.6517</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6727</v>
+        <v>-5.4765</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1408</v>
+        <v>-2.5454</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5319</v>
+        <v>-2.9312</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1982</v>
+        <v>-2.3787</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-3.1716</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1982</v>
+        <v>0.7929</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3729</v>
+        <v>0.9407</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.312</v>
+        <v>0.3765</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0609</v>
+        <v>0.5642</v>
       </c>
       <c r="V22" t="n">
-        <v>0.674</v>
+        <v>-0.4778</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.4778</v>
       </c>
       <c r="X22" t="n">
-        <v>0.674</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F. SERRANO RUBIO</t>
+          <t>G. LOPEZ TORRE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5545</v>
+        <v>-3.8108</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3074</v>
+        <v>-0.6792</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.2471</v>
+        <v>-3.1317</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.5924</v>
+        <v>-2.3567</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.9853</v>
+        <v>0.6068</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.6071</v>
+        <v>-2.9636</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0118</v>
+        <v>1.0493</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.3179</v>
+        <v>1.6079</v>
       </c>
       <c r="L23" t="n">
-        <v>1.3298</v>
+        <v>-0.5586</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.6042</v>
+        <v>-3.406</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6674</v>
+        <v>-1.001</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.9369</v>
+        <v>-2.405</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3964</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3964</v>
+        <v>0.5947</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3586</v>
+        <v>-0.3331</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3192</v>
+        <v>-0.0128</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0393</v>
+        <v>-0.3203</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>G. LOPEZ TORRE</t>
+          <t>F. SERRANO RUBIO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4501</v>
+        <v>-3.8777</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.2904</v>
+        <v>-0.7149</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.1597</v>
+        <v>-3.1629</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.3567</v>
+        <v>-3.5924</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6068</v>
+        <v>-1.9853</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.9636</v>
+        <v>-1.6071</v>
       </c>
       <c r="J24" t="n">
-        <v>1.0493</v>
+        <v>0.0118</v>
       </c>
       <c r="K24" t="n">
-        <v>1.6079</v>
+        <v>-1.3179</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5586</v>
+        <v>1.3298</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.406</v>
+        <v>-3.6042</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.001</v>
+        <v>-0.6674</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.405</v>
+        <v>-2.9369</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.3876</v>
+        <v>0.3964</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.5947</v>
+        <v>0.3964</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9724</v>
+        <v>-0.6818</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.624</v>
+        <v>-0.7267</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3484</v>
+        <v>0.0449</v>
       </c>
       <c r="V24" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Z. POPE</t>
+          <t>R. PEREIRA FERNANDES</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.632</v>
+        <v>-4.8051</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3321</v>
+        <v>-1.596</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.9641</v>
+        <v>-3.2092</v>
       </c>
       <c r="G25" t="n">
-        <v>-6.3767</v>
+        <v>-5.7736</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.22</v>
+        <v>-1.4193</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.1567</v>
+        <v>-4.3542</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.1636</v>
+        <v>-1.174</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.4119</v>
+        <v>0.249</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.7517</v>
+        <v>-1.4231</v>
       </c>
       <c r="M25" t="n">
-        <v>-4.2131</v>
+        <v>-4.5996</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.8081</v>
+        <v>-1.6684</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.405</v>
+        <v>-2.9312</v>
       </c>
       <c r="P25" t="n">
         <v>0.9911</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-0.1982</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9911</v>
+        <v>1.1893</v>
       </c>
       <c r="S25" t="n">
-        <v>1.2867</v>
+        <v>0.1735</v>
       </c>
       <c r="T25" t="n">
-        <v>1.2886</v>
+        <v>-0.2237</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0019</v>
+        <v>0.3972</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.5331</v>
+        <v>-0.1962</v>
       </c>
       <c r="W25" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.7403</v>
+        <v>-0.1962</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>R. PEREIRA FERNANDES</t>
+          <t>Z. POPE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.2968</v>
+        <v>-5.1028</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.0034</v>
+        <v>-0.2791</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.2934</v>
+        <v>-4.8237</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.7736</v>
+        <v>-6.3767</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.4193</v>
+        <v>-3.22</v>
       </c>
       <c r="I26" t="n">
-        <v>-4.3542</v>
+        <v>-3.1567</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.174</v>
+        <v>-2.1636</v>
       </c>
       <c r="K26" t="n">
-        <v>0.249</v>
+        <v>-1.4119</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.4231</v>
+        <v>-0.7517</v>
       </c>
       <c r="M26" t="n">
-        <v>-4.5996</v>
+        <v>-4.2131</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.6684</v>
+        <v>-1.8081</v>
       </c>
       <c r="O26" t="n">
-        <v>-2.9312</v>
+        <v>-2.405</v>
       </c>
       <c r="P26" t="n">
         <v>0.9911</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1893</v>
+        <v>0.9911</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.3182</v>
+        <v>0.8159</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6312</v>
+        <v>0.6774</v>
       </c>
       <c r="U26" t="n">
-        <v>0.313</v>
+        <v>0.1385</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.1962</v>
+        <v>-0.5331</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.1962</v>
+        <v>-1.7403</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-8.3179</v>
+        <v>-7.7537</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.7373</v>
+        <v>-4.5335</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.5807</v>
+        <v>-3.2202</v>
       </c>
       <c r="G27" t="n">
         <v>-6.592</v>
@@ -2560,13 +2560,13 @@
         <v>1.1893</v>
       </c>
       <c r="S27" t="n">
-        <v>0.2563</v>
+        <v>0.8205</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.3082</v>
+        <v>-0.1045</v>
       </c>
       <c r="U27" t="n">
-        <v>0.5645</v>
+        <v>0.9249000000000001</v>
       </c>
       <c r="V27" t="n">
         <v>-0</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-21.286</v>
+        <v>-20.6069</v>
       </c>
       <c r="E28" t="n">
-        <v>9.648400000000002</v>
+        <v>9.648500000000002</v>
       </c>
       <c r="F28" t="n">
-        <v>-30.9348</v>
+        <v>-30.2557</v>
       </c>
       <c r="G28" t="n">
         <v>-21.5524</v>
@@ -2617,7 +2617,7 @@
         <v>15.0155</v>
       </c>
       <c r="L28" t="n">
-        <v>2.4599</v>
+        <v>2.459899999999999</v>
       </c>
       <c r="M28" t="n">
         <v>-39.0278</v>
@@ -2638,13 +2638,13 @@
         <v>8.9199</v>
       </c>
       <c r="S28" t="n">
-        <v>3.506</v>
+        <v>4.1852</v>
       </c>
       <c r="T28" t="n">
-        <v>0.4603000000000002</v>
+        <v>0.4603000000000001</v>
       </c>
       <c r="U28" t="n">
-        <v>3.0459</v>
+        <v>3.7249</v>
       </c>
       <c r="V28" t="n">
         <v>-0.2665</v>
